--- a/Catch models/r_macarellus.xlsx
+++ b/Catch models/r_macarellus.xlsx
@@ -486,13 +486,13 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="I2">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -518,10 +518,10 @@
         <v>0.05</v>
       </c>
       <c r="H3">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="I3">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -544,13 +544,13 @@
         <v>21</v>
       </c>
       <c r="G4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H4">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="5" spans="1:9">

--- a/Catch models/r_macarellus.xlsx
+++ b/Catch models/r_macarellus.xlsx
@@ -46,7 +46,7 @@
     <t>Decapterus macarellus</t>
   </si>
   <si>
-    <t>1989-2015</t>
+    <t>1989-2023</t>
   </si>
   <si>
     <t>Euler-lotka methods</t>
